--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -11477,17 +11477,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
@@ -11509,17 +11509,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11529,29 +11529,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11561,29 +11561,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,29 +11593,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,29 +11625,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
@@ -11669,17 +11669,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11733,17 +11733,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
@@ -11797,17 +11797,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
@@ -11829,17 +11829,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11849,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,29 +11913,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,29 +11945,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,29 +11977,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12021,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -12053,17 +12053,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
@@ -12112,22 +12112,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -11477,17 +11477,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11509,17 +11509,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11529,29 +11529,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11561,29 +11561,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,29 +11593,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -11637,17 +11637,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,29 +11657,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,29 +11721,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,29 +11753,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11829,17 +11829,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11849,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,29 +11881,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,29 +11913,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,29 +11945,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11989,17 +11989,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,29 +12009,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
@@ -12053,17 +12053,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,29 +12073,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12105,29 +12105,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -11440,22 +11440,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
@@ -11477,17 +11477,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11509,17 +11509,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11546,12 +11546,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11561,29 +11561,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,29 +11593,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
@@ -11637,17 +11637,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
@@ -11669,17 +11669,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11689,29 +11689,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,29 +11721,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,29 +11753,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,29 +11785,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11829,17 +11829,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11849,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,29 +11881,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,29 +11913,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -11957,17 +11957,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11989,17 +11989,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,29 +12009,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
@@ -12053,17 +12053,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
@@ -12117,17 +12117,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -11445,17 +11445,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11465,29 +11465,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,29 +11497,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
@@ -11568,22 +11568,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,29 +11593,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -11637,17 +11637,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,29 +11657,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11689,29 +11689,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
@@ -11733,17 +11733,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,29 +11785,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11817,29 +11817,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11849,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,29 +11913,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,29 +11945,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,29 +11977,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12021,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -12058,12 +12058,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
@@ -12085,17 +12085,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -12117,17 +12117,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -10793,7 +10793,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界体验中心•北京SKP</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -10808,12 +10808,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>鸿蒙智行尊界体验中心•北京SKP</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11440,22 +11440,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11465,29 +11465,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,14 +11497,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
@@ -11546,12 +11546,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
@@ -11573,17 +11573,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,29 +11593,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -11637,17 +11637,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,29 +11657,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,29 +11721,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
@@ -11765,17 +11765,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,29 +11785,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11817,29 +11817,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11849,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11925,17 +11925,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,29 +11945,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,29 +11977,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12021,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,29 +12041,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,29 +12073,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12105,29 +12105,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -4029,14 +4029,14 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>0</v>
@@ -4050,14 +4050,14 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>0</v>
@@ -4071,14 +4071,14 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>0</v>
@@ -4092,14 +4092,14 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>0</v>
@@ -4113,14 +4113,14 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>0</v>
@@ -4134,14 +4134,14 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>0</v>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
@@ -4344,59 +4344,59 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>宾利</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="D165" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="E165" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="D166" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="E166" s="4" t="n">
-        <v>-1</v>
+      <c r="C166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -4407,59 +4407,59 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C167" s="4" t="n">
+      <c r="C169" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="D167" s="4" t="n">
+      <c r="D169" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="E167" s="4" t="n">
+      <c r="E169" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -4470,14 +4470,14 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E170" s="2" t="n">
         <v>0</v>
@@ -4491,14 +4491,14 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>0</v>
@@ -4512,14 +4512,14 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>0</v>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>0</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>0</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>0</v>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E176" s="2" t="n">
         <v>0</v>
@@ -4617,14 +4617,14 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>0</v>
@@ -4638,14 +4638,14 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="E178" s="2" t="n">
         <v>0</v>
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>0</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>0</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>0</v>
@@ -4806,14 +4806,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>0</v>
@@ -4827,14 +4827,14 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>0</v>
@@ -4848,59 +4848,59 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="C190" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D188" s="2" t="n">
+      <c r="D190" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E188" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D189" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="E189" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="D190" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="E190" s="3" t="n">
-        <v>1</v>
+      <c r="E190" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C191" s="3" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E191" s="3" t="n">
         <v>1</v>
@@ -4932,14 +4932,14 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C192" s="3" t="n">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="E192" s="3" t="n">
         <v>1</v>
@@ -4953,17 +4953,17 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="E193" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -4974,17 +4974,17 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C194" s="3" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -4995,59 +4995,59 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C195" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E195" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="D196" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="E196" s="2" t="n">
-        <v>0</v>
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D197" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E197" s="2" t="n">
-        <v>0</v>
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>小米</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -5058,14 +5058,14 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>0</v>
@@ -5079,14 +5079,14 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>0</v>
@@ -5100,14 +5100,14 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>0</v>
@@ -5121,14 +5121,14 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>0</v>
@@ -5142,14 +5142,14 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>0</v>
@@ -5163,14 +5163,14 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>0</v>
@@ -5184,14 +5184,14 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>0</v>
@@ -5205,14 +5205,14 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>0</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>0</v>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>0</v>
@@ -5268,14 +5268,14 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>0</v>
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>0</v>
@@ -5310,14 +5310,14 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>0</v>
@@ -5331,14 +5331,14 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>0</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>0</v>
@@ -5373,14 +5373,14 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>0</v>
@@ -5394,14 +5394,14 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>0</v>
@@ -5415,14 +5415,14 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>0</v>
@@ -5436,14 +5436,14 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0</v>
@@ -5457,14 +5457,14 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>0</v>
@@ -5478,14 +5478,14 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>0</v>
@@ -5499,14 +5499,14 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>0</v>
@@ -5520,14 +5520,14 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>0</v>
@@ -5541,14 +5541,14 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E221" s="2" t="n">
         <v>0</v>
@@ -5562,59 +5562,59 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="C224" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D222" s="2" t="n">
+      <c r="D224" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E222" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B223" s="3" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D223" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="E223" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D224" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E224" s="3" t="n">
-        <v>1</v>
+      <c r="E224" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -5625,59 +5625,59 @@
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>小鹏</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C225" s="3" t="n">
+      <c r="C227" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="D225" s="3" t="n">
+      <c r="D227" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="E225" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D226" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E226" s="4" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D227" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E227" s="4" t="n">
-        <v>-1</v>
+      <c r="E227" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -5688,59 +5688,59 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E228" s="4" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>沃尔沃</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E229" s="4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>沃尔沃</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="C228" s="4" t="n">
+      <c r="C230" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D228" s="4" t="n">
+      <c r="D230" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E228" s="4" t="n">
+      <c r="E230" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B229" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C229" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D229" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="E229" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>沃尔沃</t>
-        </is>
-      </c>
-      <c r="B230" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C230" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="D230" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E230" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -5751,14 +5751,14 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E231" s="2" t="n">
         <v>0</v>
@@ -5772,14 +5772,14 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>0</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E233" s="2" t="n">
         <v>0</v>
@@ -5814,14 +5814,14 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E234" s="2" t="n">
         <v>0</v>
@@ -5835,14 +5835,14 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E235" s="2" t="n">
         <v>0</v>
@@ -5856,14 +5856,14 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E236" s="2" t="n">
         <v>0</v>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>0</v>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>0</v>
@@ -5919,14 +5919,14 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E239" s="2" t="n">
         <v>0</v>
@@ -5940,14 +5940,14 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E240" s="2" t="n">
         <v>0</v>
@@ -5961,14 +5961,14 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E241" s="2" t="n">
         <v>0</v>
@@ -5982,14 +5982,14 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E242" s="2" t="n">
         <v>0</v>
@@ -6003,14 +6003,14 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E243" s="2" t="n">
         <v>0</v>
@@ -6024,14 +6024,14 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>0</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E245" s="2" t="n">
         <v>0</v>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E246" s="2" t="n">
         <v>0</v>
@@ -6087,14 +6087,14 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E247" s="2" t="n">
         <v>0</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C248" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E248" s="2" t="n">
         <v>0</v>
@@ -6129,14 +6129,14 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E249" s="2" t="n">
         <v>0</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E250" s="2" t="n">
         <v>0</v>
@@ -6171,14 +6171,14 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E251" s="2" t="n">
         <v>0</v>
@@ -6192,14 +6192,14 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>0</v>
@@ -6213,14 +6213,14 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E253" s="2" t="n">
         <v>0</v>
@@ -6234,101 +6234,101 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D254" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E254" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>沃尔沃</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D255" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E255" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>沃尔沃</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="C256" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D254" s="2" t="n">
+      <c r="D256" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E254" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="3" t="inlineStr">
+      <c r="E256" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B255" s="3" t="inlineStr">
+      <c r="B257" s="3" t="inlineStr">
         <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C255" s="3" t="n">
+      <c r="C257" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D255" s="3" t="n">
+      <c r="D257" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E255" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="3" t="inlineStr">
+      <c r="E257" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
         <is>
           <t>沃尔沃</t>
         </is>
       </c>
-      <c r="B256" s="3" t="inlineStr">
+      <c r="B258" s="3" t="inlineStr">
         <is>
           <t>贵州</t>
         </is>
       </c>
-      <c r="C256" s="3" t="n">
+      <c r="C258" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="D258" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E256" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D257" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D258" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" s="2" t="n">
-        <v>0</v>
+      <c r="E258" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C261" s="2" t="n">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C262" s="2" t="n">
@@ -6423,14 +6423,14 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C263" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E263" s="2" t="n">
         <v>0</v>
@@ -6444,14 +6444,14 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="2" t="n">
         <v>0</v>
@@ -6465,14 +6465,14 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E265" s="2" t="n">
         <v>0</v>
@@ -6486,14 +6486,14 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C266" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E266" s="2" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
@@ -6628,19 +6628,19 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C273" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E273" s="2" t="n">
         <v>0</v>
@@ -6649,19 +6649,19 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E274" s="2" t="n">
         <v>0</v>
@@ -6675,14 +6675,14 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>0</v>
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E299" s="2" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E300" s="2" t="n">
         <v>0</v>
@@ -7221,101 +7221,101 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E302" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C303" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D301" s="2" t="n">
+      <c r="D303" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E301" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="inlineStr">
+      <c r="E303" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B302" s="3" t="inlineStr">
+      <c r="B304" s="3" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="C302" s="3" t="n">
+      <c r="C304" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="D304" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="E302" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
+      <c r="E304" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B303" s="3" t="inlineStr">
+      <c r="B305" s="3" t="inlineStr">
         <is>
           <t>北京</t>
         </is>
       </c>
-      <c r="C303" s="3" t="n">
+      <c r="C305" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="D305" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="E303" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C304" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D304" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E304" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C305" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D305" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E305" s="2" t="n">
-        <v>0</v>
+      <c r="E305" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E306" s="2" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E307" s="2" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E308" s="2" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E333" s="2" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
@@ -7930,19 +7930,19 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E335" s="2" t="n">
         <v>0</v>
@@ -7951,19 +7951,19 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E336" s="2" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E337" s="2" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8523,49 +8523,49 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="inlineStr">
+      <c r="A364" s="2" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C364" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D364" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E364" s="3" t="n">
-        <v>1</v>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
@@ -8579,24 +8579,24 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E366" s="2" t="n">
-        <v>0</v>
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8712,14 +8712,14 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E372" s="2" t="n">
         <v>0</v>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C373" s="2" t="n">
@@ -8749,19 +8749,19 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E375" s="2" t="n">
         <v>0</v>
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C403" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D403" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E403" s="2" t="n">
         <v>0</v>
@@ -9379,19 +9379,19 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C404" s="2" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D404" s="2" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="E404" s="2" t="n">
         <v>0</v>
@@ -9400,19 +9400,19 @@
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C405" s="2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D405" s="2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E405" s="2" t="n">
         <v>0</v>
@@ -9426,14 +9426,14 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C406" s="2" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D406" s="2" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E406" s="2" t="n">
         <v>0</v>
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C407" s="2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D407" s="2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E407" s="2" t="n">
         <v>0</v>
@@ -9468,14 +9468,14 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C408" s="2" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D408" s="2" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="E408" s="2" t="n">
         <v>0</v>
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="D420" s="2" t="n">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="E420" s="2" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C421" s="2" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="D421" s="2" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E421" s="2" t="n">
         <v>0</v>
@@ -9762,14 +9762,14 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C422" s="2" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="D422" s="2" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
       <c r="E422" s="2" t="n">
         <v>0</v>
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>0</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>0</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>0</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>0</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>0</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>0</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>0</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>0</v>
@@ -9951,59 +9951,59 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D431" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E431" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D432" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E432" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C431" s="2" t="n">
+      <c r="C433" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D431" s="2" t="n">
+      <c r="D433" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E431" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B432" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C432" s="3" t="n">
-        <v>183</v>
-      </c>
-      <c r="D432" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="E432" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B433" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C433" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="D433" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="E433" s="3" t="n">
-        <v>2</v>
+      <c r="E433" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="434">
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="E434" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E435" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C434" s="3" t="n">
+      <c r="C436" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="D434" s="3" t="n">
+      <c r="D436" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="E434" s="3" t="n">
+      <c r="E436" s="3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11440,22 +11482,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11465,7 +11507,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -11477,17 +11519,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11497,7 +11539,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
@@ -11536,22 +11578,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11561,29 +11603,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11593,7 +11635,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
@@ -11605,17 +11647,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11625,14 +11667,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -11642,12 +11684,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11657,7 +11699,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
@@ -11696,22 +11738,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11721,29 +11763,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11753,7 +11795,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11765,17 +11807,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11785,29 +11827,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11817,29 +11859,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11849,29 +11891,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11881,29 +11923,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11913,7 +11955,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
@@ -11925,17 +11967,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11945,7 +11987,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
@@ -11957,17 +11999,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -11977,29 +12019,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12009,7 +12051,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12063,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12041,29 +12083,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12073,29 +12115,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12105,29 +12147,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12137,7 +12179,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>鸿蒙智行尊界体验中心•北京SKP</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界体验中心•北京SKP</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11482,22 +11482,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11539,29 +11539,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11603,29 +11603,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11738,22 +11738,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界体验中心•北京SKP</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>鸿蒙智行尊界体验中心•北京SKP</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11487,17 +11487,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
@@ -11578,22 +11578,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
@@ -11620,12 +11620,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11763,29 +11763,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -11482,22 +11482,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11539,29 +11539,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11571,29 +11571,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11667,14 +11667,14 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
@@ -11711,17 +11711,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车武汉蔡甸销售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -11731,29 +11731,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11795,29 +11795,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车武汉蔡甸销售展厅</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市蔡甸区凤凰路嘉禾工业园2号厂房 → 湖北省武汉市蔡甸区凤凰路嘉禾工业园4号楼</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12083,14 +12083,14 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -12100,12 +12100,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小米汽车西藏拉萨市经济技术开发区康达汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>拉贡路3号康达汽车城 → 西藏自治区拉萨经济技术开发区A区博达路5号1栋</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260907_vs_20260914.xlsx
@@ -10835,7 +10835,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京亦庄龙湖</t>
+          <t>鸿蒙智行尊界体验中心•北京SKP</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
+          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界体验中心•北京SKP</t>
+          <t>华为智能生活馆•北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区建国路89号院17号楼1-3层L18.L19.L20</t>
+          <t>北京市大兴区亦庄经济开发区博兴八路与兴海路交叉口龙湖亦庄天街A馆1F</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260803，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -11482,22 +11482,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
+          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
+          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
         </is>
       </c>
     </row>
@@ -11556,12 +11556,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
+          <t>安徽省淮南市经开区国庆东路汽配城北门向东200米 → 淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -11583,17 +11583,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车沧州开发区销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
+          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
         </is>
       </c>
     </row>
@@ -11615,17 +11615,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州宝应销售展厅</t>
+          <t>小鹏汽车西安马腾空汽车城销售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11635,29 +11635,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
+          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车沧州开发区销售服务中心</t>
+          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11667,29 +11667,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省沧州市开发区黄河路与石岗路交叉口路北 → 河北省沧州市开发区石港路71号</t>
+          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
+          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
         </is>
       </c>
     </row>
@@ -11738,22 +11738,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上海蓝鲸世界购物中心</t>
+          <t>小鹏汽车宿州白马汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
+          <t>安徽省宿州市经济开发区西昌南路东侧A522号 → 宿州市经济开发区西昌南路东侧A522号</t>
         </is>
       </c>
     </row>
@@ -11775,17 +11775,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津卫津南路销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路西段众恒新能源汽车物流园5号仓</t>
         </is>
       </c>
     </row>
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>哈尔滨机场路特斯拉中心</t>
+          <t>上海蓝鲸世界购物中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
+          <t>上海市浦东新区上海自由贸易试验区临港新片区方竹路888弄1-34号1F西中庭 → 上海市浦东新区方竹路888弄1-34号蓝鲸世界购物中心中庭1F-YX-L101</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车盐城永宁销售服务中心</t>
+          <t>小鹏汽车南京栖霞销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
+          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州市荔湾区龙溪大道服务中心</t>
+          <t>哈尔滨机场路特斯拉中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙溪大道502号自编1 → 海龙街道龙溪大道504号101</t>
+          <t>黑龙江省哈尔滨市道里区机场路161号 → 黑龙江省哈尔滨市道里区机场路161号（道里区迎宾路集中区迎宾路与三环路东北侧）</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车西安马腾空汽车城销售中心</t>
+          <t>小鹏汽车毕节碧阳大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>西安市灞桥区红旗街道临湾路219号 → 西安市雁塔区南三环与长鸣路十字马腾空国际车城一层A座10112号</t>
+          <t>贵州省毕节市碧阳大道佰润汽车公园 → 贵州省毕节市七星关区碧阳大道佰润汽车公园</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（未来广场）</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008 → 江西省赣州市南康区远洋未来广场1层</t>
+          <t>江苏省南通市开发区吉达路11号 → 南通市开发区东方汽车城吉达路11号</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
+          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
+          <t>金潭物流园1栋 → 金潭大道1号</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车长沙雨花销售服务中心</t>
+          <t>小鹏汽车盐城永宁销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
+          <t>江苏省盐城市新都路88号 → 江苏省盐城市盐都区新都路88号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车重庆融创茂文旅城销售中心</t>
+          <t>小鹏汽车长沙雨花销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>重庆市沙坪坝区西林大道84号融创茂 → 融创茂文旅城</t>
+          <t>同升街道黄谷路262-12号 → 湖南省长沙市雨花区黄谷路262号</t>
         </is>
       </c>
     </row>
@@ -12068,12 +12068,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京栖霞销售中心</t>
+          <t>小鹏汽车扬州宝应销售展厅</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>南京市栖霞区仙尧路27号 C2-1 → 仙尧路27号 C2-1</t>
+          <t>扬州市宝应县超越名车广场 → 扬州市宝应县顺达路超越名车广场</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江苏省淮安市清江浦区淮安万象城汽车体验店</t>
+          <t>小鹏汽车天津卫津南路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>翔宇大道万达广场(淮安水渡口店)西侧约40米 → 江苏淮安市清江浦区水渡口街道万象城1层L146号小米之家</t>
+          <t>天津市西青区李七庄街卫津南路绥江桥东南100米 → 天津市西青区卫津南路与绥江桥东南100米</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省赣州市章贡区金潭南大道</t>
+          <t>小米之家北京市海淀区世纪金源购物中心汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>金潭物流园1栋 → 金潭大道1号</t>
+          <t>远大路1号 → 世纪金源购物中心东区一层小米之家</t>
         </is>
       </c>
     </row>
